--- a/lorenzo-playwright-kdf/excelFramework/testcases/NursingActivity/LSTP_NursingActivity_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/NursingActivity/LSTP_NursingActivity_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\NursingActivity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E85FFBB-74C8-4389-BC52-BBCFAB722354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E69602A-21AA-435A-B9C1-2444CA320CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1335" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{5D950D6C-82D7-4427-9133-2701D8C42B23}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5D950D6C-82D7-4427-9133-2701D8C42B23}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="289">
   <si>
     <t>StepNo</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>launchUrl</t>
-  </si>
-  <si>
-    <t>http://dxcappchne8097a.cscidp.net/webclient_sso/extlogon.aspx?idp=oidnatlogon&amp;IsClientInfoNotRequired=true</t>
   </si>
   <si>
     <t>Login with valid credentials</t>
@@ -1365,25 +1362,22 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="J3" t="s">
         <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1391,13 +1385,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1405,10 +1399,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1419,16 +1413,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1436,13 +1430,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1450,16 +1444,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1467,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1481,19 +1475,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>33</v>
       </c>
-      <c r="E10" t="s">
-        <v>34</v>
-      </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1501,16 +1495,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
-      </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1518,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1532,10 +1526,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1546,16 +1540,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
         <v>39</v>
       </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>40</v>
-      </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1563,13 +1557,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
         <v>41</v>
       </c>
-      <c r="C15" t="s">
-        <v>42</v>
-      </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1577,13 +1571,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" t="s">
         <v>43</v>
       </c>
-      <c r="F16" t="s">
+      <c r="J16" t="s">
         <v>44</v>
-      </c>
-      <c r="J16" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1591,19 +1585,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
         <v>46</v>
       </c>
-      <c r="C17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>47</v>
       </c>
-      <c r="F17" t="s">
+      <c r="J17" t="s">
         <v>48</v>
-      </c>
-      <c r="J17" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1611,16 +1605,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" t="s">
         <v>50</v>
       </c>
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" t="s">
-        <v>51</v>
-      </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1628,13 +1622,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1642,10 +1636,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1656,16 +1650,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
         <v>54</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>55</v>
       </c>
-      <c r="D21" t="s">
-        <v>56</v>
-      </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1673,13 +1667,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
         <v>57</v>
       </c>
-      <c r="C22" t="s">
-        <v>58</v>
-      </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1687,19 +1681,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
         <v>59</v>
       </c>
-      <c r="C23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
+        <v>47</v>
+      </c>
+      <c r="K23" t="s">
         <v>60</v>
-      </c>
-      <c r="F23" t="s">
-        <v>48</v>
-      </c>
-      <c r="K23" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1707,19 +1701,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" t="s">
         <v>47</v>
       </c>
-      <c r="F24" t="s">
+      <c r="J24" t="s">
         <v>48</v>
-      </c>
-      <c r="J24" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1727,19 +1721,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" t="s">
         <v>63</v>
       </c>
-      <c r="C25" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
+        <v>47</v>
+      </c>
+      <c r="K25" t="s">
         <v>64</v>
-      </c>
-      <c r="F25" t="s">
-        <v>48</v>
-      </c>
-      <c r="K25" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1747,16 +1741,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1764,13 +1758,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1778,16 +1772,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" t="s">
         <v>68</v>
       </c>
-      <c r="C28" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" t="s">
-        <v>69</v>
-      </c>
       <c r="F28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1795,19 +1789,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" t="s">
         <v>70</v>
       </c>
-      <c r="C29" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
+        <v>47</v>
+      </c>
+      <c r="K29" t="s">
         <v>71</v>
-      </c>
-      <c r="F29" t="s">
-        <v>48</v>
-      </c>
-      <c r="K29" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1815,19 +1809,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" t="s">
         <v>73</v>
       </c>
-      <c r="C30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
         <v>74</v>
       </c>
-      <c r="F30" t="s">
+      <c r="K30" t="s">
         <v>75</v>
-      </c>
-      <c r="K30" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1835,19 +1829,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" t="s">
         <v>77</v>
       </c>
-      <c r="C31" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
+        <v>47</v>
+      </c>
+      <c r="K31" t="s">
         <v>78</v>
-      </c>
-      <c r="F31" t="s">
-        <v>48</v>
-      </c>
-      <c r="K31" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1855,19 +1849,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" t="s">
         <v>80</v>
       </c>
-      <c r="C32" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
+        <v>47</v>
+      </c>
+      <c r="K32" t="s">
         <v>81</v>
-      </c>
-      <c r="F32" t="s">
-        <v>48</v>
-      </c>
-      <c r="K32" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1875,19 +1869,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" t="s">
         <v>83</v>
       </c>
-      <c r="C33" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
+        <v>47</v>
+      </c>
+      <c r="K33" t="s">
         <v>84</v>
-      </c>
-      <c r="F33" t="s">
-        <v>48</v>
-      </c>
-      <c r="K33" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -1895,16 +1889,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" t="s">
         <v>86</v>
       </c>
-      <c r="C34" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" t="s">
-        <v>87</v>
-      </c>
       <c r="F34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -1912,13 +1906,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1926,19 +1920,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" t="s">
         <v>89</v>
       </c>
-      <c r="C36" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s">
         <v>90</v>
-      </c>
-      <c r="F36" t="s">
-        <v>75</v>
-      </c>
-      <c r="K36" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -1946,19 +1940,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" t="s">
         <v>92</v>
       </c>
-      <c r="C37" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s">
         <v>93</v>
-      </c>
-      <c r="F37" t="s">
-        <v>75</v>
-      </c>
-      <c r="K37" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -1966,19 +1960,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" t="s">
         <v>95</v>
       </c>
-      <c r="C38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s">
         <v>96</v>
-      </c>
-      <c r="F38" t="s">
-        <v>75</v>
-      </c>
-      <c r="K38" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -1986,19 +1980,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" t="s">
         <v>98</v>
       </c>
-      <c r="C39" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="F39" t="s">
+        <v>74</v>
+      </c>
+      <c r="K39" t="s">
         <v>99</v>
-      </c>
-      <c r="F39" t="s">
-        <v>75</v>
-      </c>
-      <c r="K39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2006,19 +2000,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" t="s">
         <v>101</v>
       </c>
-      <c r="C40" t="s">
-        <v>58</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
+        <v>74</v>
+      </c>
+      <c r="K40" t="s">
         <v>102</v>
-      </c>
-      <c r="F40" t="s">
-        <v>75</v>
-      </c>
-      <c r="K40" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2026,19 +2020,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" t="s">
         <v>104</v>
       </c>
-      <c r="C41" t="s">
-        <v>58</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="F41" t="s">
+        <v>74</v>
+      </c>
+      <c r="K41" t="s">
         <v>105</v>
-      </c>
-      <c r="F41" t="s">
-        <v>75</v>
-      </c>
-      <c r="K41" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -2046,16 +2040,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" t="s">
         <v>107</v>
       </c>
-      <c r="C42" t="s">
-        <v>58</v>
-      </c>
-      <c r="D42" t="s">
-        <v>108</v>
-      </c>
       <c r="F42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2063,13 +2057,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" t="s">
         <v>109</v>
       </c>
-      <c r="C43" t="s">
-        <v>110</v>
-      </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2077,19 +2071,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" t="s">
         <v>111</v>
       </c>
-      <c r="C44" t="s">
-        <v>110</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="F44" t="s">
         <v>112</v>
       </c>
-      <c r="F44" t="s">
+      <c r="J44" t="s">
         <v>113</v>
-      </c>
-      <c r="J44" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2097,22 +2091,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F45" t="s">
         <v>115</v>
       </c>
-      <c r="C45" t="s">
-        <v>110</v>
-      </c>
-      <c r="D45" t="s">
-        <v>112</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>116</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>117</v>
-      </c>
-      <c r="H45" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2120,16 +2114,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" t="s">
         <v>119</v>
       </c>
-      <c r="C46" t="s">
-        <v>110</v>
-      </c>
-      <c r="D46" t="s">
-        <v>120</v>
-      </c>
       <c r="F46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2137,10 +2131,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -2151,13 +2145,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>121</v>
+      </c>
+      <c r="C48" t="s">
         <v>122</v>
       </c>
-      <c r="C48" t="s">
-        <v>123</v>
-      </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2165,19 +2159,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>123</v>
+      </c>
+      <c r="C49" t="s">
+        <v>122</v>
+      </c>
+      <c r="D49" t="s">
         <v>124</v>
       </c>
-      <c r="C49" t="s">
-        <v>123</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="F49" t="s">
+        <v>47</v>
+      </c>
+      <c r="K49" t="s">
         <v>125</v>
-      </c>
-      <c r="F49" t="s">
-        <v>48</v>
-      </c>
-      <c r="K49" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2185,19 +2179,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50" t="s">
+        <v>122</v>
+      </c>
+      <c r="D50" t="s">
         <v>127</v>
       </c>
-      <c r="C50" t="s">
-        <v>123</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="F50" t="s">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s">
         <v>128</v>
-      </c>
-      <c r="F50" t="s">
-        <v>75</v>
-      </c>
-      <c r="K50" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2205,19 +2199,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>129</v>
+      </c>
+      <c r="C51" t="s">
+        <v>122</v>
+      </c>
+      <c r="D51" t="s">
         <v>130</v>
       </c>
-      <c r="C51" t="s">
-        <v>123</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="F51" t="s">
+        <v>74</v>
+      </c>
+      <c r="K51" t="s">
         <v>131</v>
-      </c>
-      <c r="F51" t="s">
-        <v>75</v>
-      </c>
-      <c r="K51" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2225,19 +2219,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C52" t="s">
+        <v>122</v>
+      </c>
+      <c r="D52" t="s">
         <v>133</v>
       </c>
-      <c r="C52" t="s">
-        <v>123</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
+        <v>74</v>
+      </c>
+      <c r="K52" t="s">
         <v>134</v>
-      </c>
-      <c r="F52" t="s">
-        <v>75</v>
-      </c>
-      <c r="K52" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2245,19 +2239,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>135</v>
+      </c>
+      <c r="C53" t="s">
+        <v>122</v>
+      </c>
+      <c r="D53" t="s">
         <v>136</v>
       </c>
-      <c r="C53" t="s">
-        <v>123</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
+        <v>74</v>
+      </c>
+      <c r="K53" t="s">
         <v>137</v>
-      </c>
-      <c r="F53" t="s">
-        <v>75</v>
-      </c>
-      <c r="K53" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2265,19 +2259,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>138</v>
+      </c>
+      <c r="C54" t="s">
+        <v>122</v>
+      </c>
+      <c r="D54" t="s">
         <v>139</v>
       </c>
-      <c r="C54" t="s">
-        <v>123</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
+        <v>74</v>
+      </c>
+      <c r="K54" t="s">
         <v>140</v>
-      </c>
-      <c r="F54" t="s">
-        <v>75</v>
-      </c>
-      <c r="K54" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2285,19 +2279,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>141</v>
+      </c>
+      <c r="C55" t="s">
+        <v>122</v>
+      </c>
+      <c r="D55" t="s">
         <v>142</v>
       </c>
-      <c r="C55" t="s">
-        <v>123</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="F55" t="s">
+        <v>74</v>
+      </c>
+      <c r="K55" t="s">
         <v>143</v>
-      </c>
-      <c r="F55" t="s">
-        <v>75</v>
-      </c>
-      <c r="K55" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2305,16 +2299,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>144</v>
+      </c>
+      <c r="C56" t="s">
+        <v>122</v>
+      </c>
+      <c r="D56" t="s">
         <v>145</v>
       </c>
-      <c r="C56" t="s">
-        <v>123</v>
-      </c>
-      <c r="D56" t="s">
-        <v>146</v>
-      </c>
       <c r="F56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2322,13 +2316,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2336,19 +2330,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>147</v>
+      </c>
+      <c r="C58" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" t="s">
         <v>148</v>
       </c>
-      <c r="C58" t="s">
-        <v>31</v>
-      </c>
-      <c r="D58" t="s">
-        <v>149</v>
-      </c>
       <c r="E58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F58" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2356,16 +2350,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -2373,13 +2367,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2387,16 +2381,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -2404,13 +2398,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
+        <v>152</v>
+      </c>
+      <c r="C62" t="s">
         <v>153</v>
       </c>
-      <c r="C62" t="s">
-        <v>154</v>
-      </c>
       <c r="F62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -2418,22 +2412,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>154</v>
+      </c>
+      <c r="C63" t="s">
+        <v>153</v>
+      </c>
+      <c r="D63" t="s">
         <v>155</v>
       </c>
-      <c r="C63" t="s">
-        <v>154</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="F63" t="s">
+        <v>115</v>
+      </c>
+      <c r="G63" t="s">
         <v>156</v>
       </c>
-      <c r="F63" t="s">
-        <v>116</v>
-      </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>157</v>
-      </c>
-      <c r="H63" t="s">
-        <v>158</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
@@ -2444,10 +2438,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -2458,16 +2452,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D65" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F65" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2475,13 +2469,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2489,10 +2483,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -2503,16 +2497,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>162</v>
+      </c>
+      <c r="C68" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" t="s">
         <v>163</v>
       </c>
-      <c r="C68" t="s">
-        <v>24</v>
-      </c>
-      <c r="D68" t="s">
-        <v>164</v>
-      </c>
       <c r="F68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -2520,13 +2514,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>164</v>
+      </c>
+      <c r="C69" t="s">
         <v>165</v>
       </c>
-      <c r="C69" t="s">
-        <v>166</v>
-      </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -2534,19 +2528,19 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>166</v>
+      </c>
+      <c r="C70" t="s">
+        <v>165</v>
+      </c>
+      <c r="D70" t="s">
         <v>167</v>
       </c>
-      <c r="C70" t="s">
-        <v>166</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="F70" t="s">
+        <v>74</v>
+      </c>
+      <c r="K70" t="s">
         <v>168</v>
-      </c>
-      <c r="F70" t="s">
-        <v>75</v>
-      </c>
-      <c r="K70" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -2554,19 +2548,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>169</v>
+      </c>
+      <c r="C71" t="s">
+        <v>165</v>
+      </c>
+      <c r="D71" t="s">
         <v>170</v>
       </c>
-      <c r="C71" t="s">
-        <v>166</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="F71" t="s">
+        <v>47</v>
+      </c>
+      <c r="K71" t="s">
         <v>171</v>
-      </c>
-      <c r="F71" t="s">
-        <v>48</v>
-      </c>
-      <c r="K71" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -2574,19 +2568,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>172</v>
+      </c>
+      <c r="C72" t="s">
+        <v>165</v>
+      </c>
+      <c r="D72" t="s">
         <v>173</v>
       </c>
-      <c r="C72" t="s">
-        <v>166</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="F72" t="s">
+        <v>74</v>
+      </c>
+      <c r="K72" t="s">
         <v>174</v>
-      </c>
-      <c r="F72" t="s">
-        <v>75</v>
-      </c>
-      <c r="K72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -2594,16 +2588,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>175</v>
+      </c>
+      <c r="C73" t="s">
+        <v>165</v>
+      </c>
+      <c r="D73" t="s">
         <v>176</v>
       </c>
-      <c r="C73" t="s">
-        <v>166</v>
-      </c>
-      <c r="D73" t="s">
-        <v>177</v>
-      </c>
       <c r="F73" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -2611,13 +2605,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C74" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -2625,16 +2619,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>178</v>
+      </c>
+      <c r="C75" t="s">
+        <v>165</v>
+      </c>
+      <c r="D75" t="s">
         <v>179</v>
       </c>
-      <c r="C75" t="s">
-        <v>166</v>
-      </c>
-      <c r="D75" t="s">
-        <v>180</v>
-      </c>
       <c r="F75" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -2642,13 +2636,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F76" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -2656,10 +2650,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F77" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -2670,16 +2664,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>182</v>
+      </c>
+      <c r="C78" t="s">
+        <v>23</v>
+      </c>
+      <c r="D78" t="s">
         <v>183</v>
       </c>
-      <c r="C78" t="s">
-        <v>24</v>
-      </c>
-      <c r="D78" t="s">
-        <v>184</v>
-      </c>
       <c r="F78" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -2687,13 +2681,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>184</v>
+      </c>
+      <c r="C79" t="s">
         <v>185</v>
       </c>
-      <c r="C79" t="s">
-        <v>186</v>
-      </c>
       <c r="F79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -2701,19 +2695,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>186</v>
+      </c>
+      <c r="C80" t="s">
+        <v>185</v>
+      </c>
+      <c r="D80" t="s">
         <v>187</v>
       </c>
-      <c r="C80" t="s">
-        <v>186</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="F80" t="s">
+        <v>74</v>
+      </c>
+      <c r="K80" t="s">
         <v>188</v>
-      </c>
-      <c r="F80" t="s">
-        <v>75</v>
-      </c>
-      <c r="K80" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2721,19 +2715,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>189</v>
+      </c>
+      <c r="C81" t="s">
+        <v>185</v>
+      </c>
+      <c r="D81" t="s">
         <v>190</v>
       </c>
-      <c r="C81" t="s">
-        <v>186</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="F81" t="s">
+        <v>74</v>
+      </c>
+      <c r="K81" t="s">
         <v>191</v>
-      </c>
-      <c r="F81" t="s">
-        <v>75</v>
-      </c>
-      <c r="K81" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2741,16 +2735,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C82" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F82" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2758,13 +2752,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C83" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -2772,16 +2766,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C84" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D84" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F84" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -2789,13 +2783,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C85" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2803,10 +2797,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F86" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -2817,16 +2811,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>197</v>
+      </c>
+      <c r="C87" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" t="s">
         <v>198</v>
       </c>
-      <c r="C87" t="s">
-        <v>24</v>
-      </c>
-      <c r="D87" t="s">
-        <v>199</v>
-      </c>
       <c r="F87" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2834,13 +2828,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>199</v>
+      </c>
+      <c r="C88" t="s">
         <v>200</v>
       </c>
-      <c r="C88" t="s">
-        <v>201</v>
-      </c>
       <c r="F88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -2848,16 +2842,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>201</v>
+      </c>
+      <c r="C89" t="s">
+        <v>200</v>
+      </c>
+      <c r="D89" t="s">
         <v>202</v>
       </c>
-      <c r="C89" t="s">
-        <v>201</v>
-      </c>
-      <c r="D89" t="s">
-        <v>203</v>
-      </c>
       <c r="F89" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -2865,13 +2859,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>203</v>
+      </c>
+      <c r="C90" t="s">
         <v>204</v>
       </c>
-      <c r="C90" t="s">
-        <v>205</v>
-      </c>
       <c r="F90" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -2879,10 +2873,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F91" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -2893,16 +2887,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>206</v>
+      </c>
+      <c r="C92" t="s">
+        <v>204</v>
+      </c>
+      <c r="D92" t="s">
         <v>207</v>
       </c>
-      <c r="C92" t="s">
-        <v>205</v>
-      </c>
-      <c r="D92" t="s">
-        <v>208</v>
-      </c>
       <c r="F92" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -2910,13 +2904,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C93" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -2924,22 +2918,22 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C94" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D94" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F94" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G94" t="s">
+        <v>156</v>
+      </c>
+      <c r="H94" t="s">
         <v>157</v>
-      </c>
-      <c r="H94" t="s">
-        <v>158</v>
       </c>
       <c r="J94" t="b">
         <v>1</v>
@@ -2950,10 +2944,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F95" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J95">
         <v>1</v>
@@ -2964,16 +2958,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
+        <v>211</v>
+      </c>
+      <c r="C96" t="s">
+        <v>204</v>
+      </c>
+      <c r="D96" t="s">
         <v>212</v>
       </c>
-      <c r="C96" t="s">
-        <v>205</v>
-      </c>
-      <c r="D96" t="s">
-        <v>213</v>
-      </c>
       <c r="F96" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -2981,13 +2975,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C97" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -2995,22 +2989,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C98" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D98" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F98" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G98" t="s">
+        <v>156</v>
+      </c>
+      <c r="H98" t="s">
         <v>157</v>
-      </c>
-      <c r="H98" t="s">
-        <v>158</v>
       </c>
       <c r="J98" t="b">
         <v>1</v>
@@ -3021,10 +3015,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F99" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J99">
         <v>1</v>
@@ -3035,16 +3029,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>216</v>
+      </c>
+      <c r="C100" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" t="s">
         <v>217</v>
       </c>
-      <c r="C100" t="s">
-        <v>19</v>
-      </c>
-      <c r="D100" t="s">
-        <v>218</v>
-      </c>
       <c r="F100" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -3052,16 +3046,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>218</v>
+      </c>
+      <c r="C101" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" t="s">
         <v>219</v>
       </c>
-      <c r="C101" t="s">
-        <v>19</v>
-      </c>
-      <c r="D101" t="s">
-        <v>220</v>
-      </c>
       <c r="F101" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -3069,13 +3063,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F102" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3117,93 +3111,93 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B2" t="s">
         <v>222</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>223</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>224</v>
-      </c>
-      <c r="D2" t="s">
-        <v>225</v>
       </c>
       <c r="E2">
         <v>1234567890</v>
@@ -3212,61 +3206,61 @@
         <v>7700900000</v>
       </c>
       <c r="G2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H2" t="s">
         <v>226</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>224</v>
+      </c>
+      <c r="J2" t="s">
         <v>227</v>
       </c>
-      <c r="I2" t="s">
-        <v>225</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>228</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>228</v>
+      </c>
+      <c r="M2" t="s">
         <v>229</v>
       </c>
-      <c r="L2" t="s">
-        <v>229</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>230</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>231</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>232</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>233</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>234</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>235</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>236</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>237</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>238</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>239</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>240</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>241</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3285,71 +3279,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B9" s="3">
         <v>101</v>
@@ -3357,7 +3351,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B10" s="3">
         <v>14</v>
@@ -3365,7 +3359,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B11" s="3">
         <v>51</v>
@@ -3373,15 +3367,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
@@ -3389,7 +3383,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
@@ -3397,31 +3391,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>265</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>269</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B18" s="3">
         <v>4</v>
@@ -3429,18 +3423,18 @@
     </row>
     <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>274</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3460,71 +3454,77 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C2" t="s">
         <v>279</v>
-      </c>
-      <c r="C2" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3" t="s">
         <v>281</v>
-      </c>
-      <c r="C3" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" t="s">
         <v>283</v>
       </c>
-      <c r="B4" t="s">
-        <v>284</v>
-      </c>
       <c r="C4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5" t="s">
         <v>285</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>286</v>
-      </c>
-      <c r="C5" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" t="s">
         <v>288</v>
       </c>
-      <c r="B6" t="s">
-        <v>289</v>
-      </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a4153a30-97aa-49dd-8839-66f72081522c}" enabled="1" method="Standard" siteId="{9ffff5c3-bdfa-4a9d-b595-ff68329945ef}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/lorenzo-playwright-kdf/excelFramework/testcases/NursingActivity/LSTP_NursingActivity_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/NursingActivity/LSTP_NursingActivity_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\NursingActivity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E69602A-21AA-435A-B9C1-2444CA320CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49312240-4E6C-4F01-924C-645E6A21F1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5D950D6C-82D7-4427-9133-2701D8C42B23}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="290">
   <si>
     <t>StepNo</t>
   </si>
@@ -906,6 +906,9 @@
   </si>
   <si>
     <t>Login password</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -1659,7 +1662,7 @@
         <v>55</v>
       </c>
       <c r="F21" t="s">
-        <v>25</v>
+        <v>289</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -2049,7 +2052,7 @@
         <v>107</v>
       </c>
       <c r="F42" t="s">
-        <v>25</v>
+        <v>289</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2123,7 +2126,7 @@
         <v>119</v>
       </c>
       <c r="F46" t="s">
-        <v>25</v>
+        <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">

--- a/lorenzo-playwright-kdf/excelFramework/testcases/NursingActivity/LSTP_NursingActivity_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/NursingActivity/LSTP_NursingActivity_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\NursingActivity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49312240-4E6C-4F01-924C-645E6A21F1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576813CA-1377-413D-8D3C-36A8D2516466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5D950D6C-82D7-4427-9133-2701D8C42B23}"/>
   </bookViews>
@@ -272,27 +272,18 @@
     <t>Enter Home Telephone number</t>
   </si>
   <si>
-    <t>txt_ TelephoneHome</t>
-  </si>
-  <si>
     <t>TELEPHONEHOME</t>
   </si>
   <si>
     <t>Enter Mobile Telephone number</t>
   </si>
   <si>
-    <t>txt_ TelephoneMobile</t>
-  </si>
-  <si>
     <t>TELEPHONEMOBILE</t>
   </si>
   <si>
     <t>Enter Email address</t>
   </si>
   <si>
-    <t>txt_ TelephoneEmail</t>
-  </si>
-  <si>
     <t>EMAIL</t>
   </si>
   <si>
@@ -909,6 +900,15 @@
   </si>
   <si>
     <t>launchRegistration</t>
+  </si>
+  <si>
+    <t>txt_TelephoneHome</t>
+  </si>
+  <si>
+    <t>txt_TelephoneMobile</t>
+  </si>
+  <si>
+    <t>txt_TelephoneEmail</t>
   </si>
 </sst>
 </file>
@@ -1662,7 +1662,7 @@
         <v>55</v>
       </c>
       <c r="F21" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1838,13 +1838,13 @@
         <v>57</v>
       </c>
       <c r="D31" t="s">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="F31" t="s">
         <v>47</v>
       </c>
       <c r="K31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1852,19 +1852,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
         <v>57</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>288</v>
       </c>
       <c r="F32" t="s">
         <v>47</v>
       </c>
       <c r="K32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1872,19 +1872,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
         <v>57</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="F33" t="s">
         <v>47</v>
       </c>
       <c r="K33" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -1892,13 +1892,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
         <v>57</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -1909,7 +1909,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C35" t="s">
         <v>57</v>
@@ -1923,19 +1923,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
         <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F36" t="s">
         <v>74</v>
       </c>
       <c r="K36" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -1943,19 +1943,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
         <v>57</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F37" t="s">
         <v>74</v>
       </c>
       <c r="K37" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -1963,19 +1963,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
         <v>57</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F38" t="s">
         <v>74</v>
       </c>
       <c r="K38" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -1983,19 +1983,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
         <v>57</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F39" t="s">
         <v>74</v>
       </c>
       <c r="K39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2003,19 +2003,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C40" t="s">
         <v>57</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F40" t="s">
         <v>74</v>
       </c>
       <c r="K40" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2023,19 +2023,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
         <v>57</v>
       </c>
       <c r="D41" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F41" t="s">
         <v>74</v>
       </c>
       <c r="K41" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -2043,16 +2043,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
         <v>57</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F42" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2060,10 +2060,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F43" t="s">
         <v>19</v>
@@ -2074,19 +2074,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F44" t="s">
+        <v>109</v>
+      </c>
+      <c r="J44" t="s">
         <v>110</v>
-      </c>
-      <c r="C44" t="s">
-        <v>109</v>
-      </c>
-      <c r="D44" t="s">
-        <v>111</v>
-      </c>
-      <c r="F44" t="s">
-        <v>112</v>
-      </c>
-      <c r="J44" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2094,22 +2094,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" t="s">
+        <v>108</v>
+      </c>
+      <c r="F45" t="s">
+        <v>112</v>
+      </c>
+      <c r="G45" t="s">
+        <v>113</v>
+      </c>
+      <c r="H45" t="s">
         <v>114</v>
-      </c>
-      <c r="C45" t="s">
-        <v>109</v>
-      </c>
-      <c r="D45" t="s">
-        <v>111</v>
-      </c>
-      <c r="F45" t="s">
-        <v>115</v>
-      </c>
-      <c r="G45" t="s">
-        <v>116</v>
-      </c>
-      <c r="H45" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2117,16 +2117,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D46" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F46" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2134,7 +2134,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F47" t="s">
         <v>21</v>
@@ -2148,10 +2148,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C48" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F48" t="s">
         <v>19</v>
@@ -2162,19 +2162,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F49" t="s">
         <v>47</v>
       </c>
       <c r="K49" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2182,19 +2182,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D50" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F50" t="s">
         <v>74</v>
       </c>
       <c r="K50" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2202,19 +2202,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C51" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D51" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F51" t="s">
         <v>74</v>
       </c>
       <c r="K51" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2222,19 +2222,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D52" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F52" t="s">
         <v>74</v>
       </c>
       <c r="K52" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2242,19 +2242,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C53" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D53" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F53" t="s">
         <v>74</v>
       </c>
       <c r="K53" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2262,19 +2262,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C54" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F54" t="s">
         <v>74</v>
       </c>
       <c r="K54" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2282,19 +2282,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C55" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D55" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F55" t="s">
         <v>74</v>
       </c>
       <c r="K55" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2302,13 +2302,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D56" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F56" t="s">
         <v>25</v>
@@ -2319,7 +2319,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C57" t="s">
         <v>30</v>
@@ -2333,13 +2333,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C58" t="s">
         <v>30</v>
       </c>
       <c r="D58" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E58" t="s">
         <v>33</v>
@@ -2353,7 +2353,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C59" t="s">
         <v>30</v>
@@ -2370,10 +2370,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F60" t="s">
         <v>19</v>
@@ -2384,13 +2384,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D61" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F61" t="s">
         <v>25</v>
@@ -2401,10 +2401,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C62" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F62" t="s">
         <v>19</v>
@@ -2415,22 +2415,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>151</v>
+      </c>
+      <c r="C63" t="s">
+        <v>150</v>
+      </c>
+      <c r="D63" t="s">
+        <v>152</v>
+      </c>
+      <c r="F63" t="s">
+        <v>112</v>
+      </c>
+      <c r="G63" t="s">
+        <v>153</v>
+      </c>
+      <c r="H63" t="s">
         <v>154</v>
-      </c>
-      <c r="C63" t="s">
-        <v>153</v>
-      </c>
-      <c r="D63" t="s">
-        <v>155</v>
-      </c>
-      <c r="F63" t="s">
-        <v>115</v>
-      </c>
-      <c r="G63" t="s">
-        <v>156</v>
-      </c>
-      <c r="H63" t="s">
-        <v>157</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
@@ -2441,7 +2441,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F64" t="s">
         <v>21</v>
@@ -2455,13 +2455,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C65" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D65" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F65" t="s">
         <v>25</v>
@@ -2472,7 +2472,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C66" t="s">
         <v>23</v>
@@ -2486,7 +2486,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F67" t="s">
         <v>21</v>
@@ -2500,13 +2500,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F68" t="s">
         <v>25</v>
@@ -2517,10 +2517,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C69" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F69" t="s">
         <v>19</v>
@@ -2531,19 +2531,19 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C70" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D70" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F70" t="s">
         <v>74</v>
       </c>
       <c r="K70" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -2551,19 +2551,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C71" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D71" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F71" t="s">
         <v>47</v>
       </c>
       <c r="K71" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -2571,19 +2571,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C72" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F72" t="s">
         <v>74</v>
       </c>
       <c r="K72" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -2591,13 +2591,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C73" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D73" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F73" t="s">
         <v>25</v>
@@ -2608,10 +2608,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C74" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F74" t="s">
         <v>19</v>
@@ -2622,13 +2622,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C75" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D75" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F75" t="s">
         <v>25</v>
@@ -2639,7 +2639,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -2653,7 +2653,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F77" t="s">
         <v>21</v>
@@ -2667,13 +2667,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C78" t="s">
         <v>23</v>
       </c>
       <c r="D78" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F78" t="s">
         <v>25</v>
@@ -2684,10 +2684,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C79" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F79" t="s">
         <v>19</v>
@@ -2698,19 +2698,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C80" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D80" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F80" t="s">
         <v>74</v>
       </c>
       <c r="K80" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2718,19 +2718,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C81" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D81" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F81" t="s">
         <v>74</v>
       </c>
       <c r="K81" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2738,13 +2738,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C82" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D82" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F82" t="s">
         <v>25</v>
@@ -2755,10 +2755,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C83" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F83" t="s">
         <v>19</v>
@@ -2769,13 +2769,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C84" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D84" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F84" t="s">
         <v>25</v>
@@ -2786,7 +2786,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
@@ -2800,7 +2800,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F86" t="s">
         <v>21</v>
@@ -2814,13 +2814,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F87" t="s">
         <v>25</v>
@@ -2831,10 +2831,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C88" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F88" t="s">
         <v>19</v>
@@ -2845,13 +2845,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C89" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D89" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F89" t="s">
         <v>25</v>
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C90" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F90" t="s">
         <v>19</v>
@@ -2876,7 +2876,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F91" t="s">
         <v>21</v>
@@ -2890,13 +2890,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C92" t="s">
+        <v>201</v>
+      </c>
+      <c r="D92" t="s">
         <v>204</v>
-      </c>
-      <c r="D92" t="s">
-        <v>207</v>
       </c>
       <c r="F92" t="s">
         <v>25</v>
@@ -2907,10 +2907,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C93" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F93" t="s">
         <v>19</v>
@@ -2921,22 +2921,22 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C94" t="s">
+        <v>201</v>
+      </c>
+      <c r="D94" t="s">
         <v>204</v>
       </c>
-      <c r="D94" t="s">
-        <v>207</v>
-      </c>
       <c r="F94" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G94" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H94" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J94" t="b">
         <v>1</v>
@@ -2947,7 +2947,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F95" t="s">
         <v>21</v>
@@ -2961,13 +2961,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C96" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D96" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F96" t="s">
         <v>25</v>
@@ -2978,10 +2978,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F97" t="s">
         <v>19</v>
@@ -2992,22 +2992,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C98" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D98" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F98" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G98" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H98" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J98" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F99" t="s">
         <v>21</v>
@@ -3032,13 +3032,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F100" t="s">
         <v>25</v>
@@ -3049,13 +3049,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C101" t="s">
         <v>18</v>
       </c>
       <c r="D101" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F101" t="s">
         <v>25</v>
@@ -3066,7 +3066,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C102" t="s">
         <v>14</v>
@@ -3126,81 +3126,81 @@
         <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="N1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="U1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="X1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D2" t="s">
         <v>221</v>
-      </c>
-      <c r="B2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D2" t="s">
-        <v>224</v>
       </c>
       <c r="E2">
         <v>1234567890</v>
@@ -3209,61 +3209,61 @@
         <v>7700900000</v>
       </c>
       <c r="G2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I2" t="s">
+        <v>221</v>
+      </c>
+      <c r="J2" t="s">
+        <v>224</v>
+      </c>
+      <c r="K2" t="s">
         <v>225</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
+        <v>225</v>
+      </c>
+      <c r="M2" t="s">
         <v>226</v>
       </c>
-      <c r="I2" t="s">
-        <v>224</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="N2" t="s">
         <v>227</v>
       </c>
-      <c r="K2" t="s">
+      <c r="O2" t="s">
         <v>228</v>
       </c>
-      <c r="L2" t="s">
-        <v>228</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="P2" t="s">
         <v>229</v>
       </c>
-      <c r="N2" t="s">
+      <c r="Q2" t="s">
         <v>230</v>
       </c>
-      <c r="O2" t="s">
+      <c r="R2" t="s">
         <v>231</v>
       </c>
-      <c r="P2" t="s">
+      <c r="S2" t="s">
         <v>232</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="T2" t="s">
         <v>233</v>
       </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>234</v>
       </c>
-      <c r="S2" t="s">
+      <c r="V2" t="s">
         <v>235</v>
       </c>
-      <c r="T2" t="s">
+      <c r="W2" t="s">
         <v>236</v>
       </c>
-      <c r="U2" t="s">
+      <c r="X2" t="s">
         <v>237</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Y2" t="s">
         <v>238</v>
-      </c>
-      <c r="W2" t="s">
-        <v>239</v>
-      </c>
-      <c r="X2" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -3282,71 +3282,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B9" s="3">
         <v>101</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B10" s="3">
         <v>14</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B11" s="3">
         <v>51</v>
@@ -3370,15 +3370,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
@@ -3386,7 +3386,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
@@ -3394,31 +3394,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B18" s="3">
         <v>4</v>
@@ -3426,18 +3426,18 @@
     </row>
     <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -3457,13 +3457,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -3471,54 +3471,54 @@
         <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
